--- a/Task3/Таблица ответственности компонентов.xlsx
+++ b/Task3/Таблица ответственности компонентов.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sergej/Documents/GitHub/Solution-AI-Sprint7/Task3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BC37BA9-0D4A-F04F-8CFD-1EEF3329FF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03DB1DD-B81D-004D-B9C2-D235662CAFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="42480" yWindow="9280" windowWidth="28240" windowHeight="17240" xr2:uid="{44045256-3BFE-5A45-BDE8-02D2B0654DC3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>Описание выходного контракта</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Ответственность системы</t>
   </si>
   <si>
-    <t>Определение проблемной транзакции</t>
-  </si>
-  <si>
     <t>Ответственность на модели</t>
   </si>
   <si>
@@ -80,12 +77,6 @@
     <t>Модель определяет значение данного признака</t>
   </si>
   <si>
-    <t>На основании бизнеса</t>
-  </si>
-  <si>
-    <t>Транзакция является не проблемной и проходит успешно</t>
-  </si>
-  <si>
     <t>Ссылка на транзакцию</t>
   </si>
   <si>
@@ -141,6 +132,39 @@
   </si>
   <si>
     <t>Руководитель экспертизы</t>
+  </si>
+  <si>
+    <t>На основании обучения на истории проблемных операций</t>
+  </si>
+  <si>
+    <t>Транзакция уходит в сервис правил для проверки, далее приоритезациия и на разбор сотруднику банка</t>
+  </si>
+  <si>
+    <t>Граница доверия</t>
+  </si>
+  <si>
+    <t>Меры защиты</t>
+  </si>
+  <si>
+    <t>Финальное решение за сотрудником а не моделью</t>
+  </si>
+  <si>
+    <t>Модель проставляет только признаки и приоритеты</t>
+  </si>
+  <si>
+    <t>Модель может ошибится в части транзакций с маркетплейсов (например)</t>
+  </si>
+  <si>
+    <t>запускать модель обучаться на определенных сегментах (транзакции от маркет плейсов например)</t>
+  </si>
+  <si>
+    <t>Ответственность в любом случае за банком</t>
+  </si>
+  <si>
+    <t>По факту модель дает только рекомендацию. Все решения должны быть зафиксированы в аудите</t>
+  </si>
+  <si>
+    <t>Определение проблемной транзакции и прстановка признака и приоритета</t>
   </si>
 </sst>
 </file>
@@ -205,22 +229,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -556,20 +587,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5F6209-8ABA-A54A-95A5-F7CD50E31C47}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.6640625" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="1" max="1" width="51" customWidth="1"/>
+    <col min="2" max="2" width="36.83203125" customWidth="1"/>
     <col min="3" max="3" width="34.83203125" customWidth="1"/>
     <col min="4" max="4" width="37" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5"/>
+      <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -579,137 +610,195 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="3" t="s">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+    </row>
+    <row r="15" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="B18" s="7"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="1" t="s">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="7" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+      <c r="B22" s="7"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="B23" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+      <c r="C23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="4"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="2" t="s">
+    </row>
+    <row r="24" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="B24" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="C24" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+      <c r="D24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="6" t="s">
+    </row>
+    <row r="25" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="B25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="C25" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="102" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+      <c r="D25" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
